--- a/position_model/datasets/dataset_for_position.xlsx
+++ b/position_model/datasets/dataset_for_position.xlsx
@@ -52,18 +52,12 @@
     <t>CR000001.dcm</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250403090444/series_004_3_CR/DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>8feee3d90284b5919cfe3dffde2fa651</t>
   </si>
   <si>
     <t>CR000002.dcm</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250403090444/series_004_3_CR/DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>fe69d2d49a6230809c0c446814d7b5ea</t>
   </si>
   <si>
@@ -73,15 +67,9 @@
     <t>series_003_3_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250403092052/series_003_3_CR/DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>c7f91915ec62ef6720f566082631a723</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250403092052/series_003_3_CR/DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>c0a97e31d443c3d6c44d41aae95bdc67</t>
   </si>
   <si>
@@ -91,15 +79,9 @@
     <t>series_001_2_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250407113211/series_001_2_CR/DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>bf7a9124bf1df1b470e5824522af60e1</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/1.2.840.113619.2.110.512719.20250407113211/series_001_2_CR/DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>0c6bf17013f8c2bc9af8d4a145090d54</t>
   </si>
   <si>
@@ -112,15 +94,9 @@
     <t>series_003_2_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.10245777060263212829333021434108890537/series_003_2_CR/A2504412435 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>ba500c5481e525546f2de2d3185dd766</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.10245777060263212829333021434108890537/series_003_2_CR/A2504412435 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>622a4460cbbdb7093d3ddaae37ca93f6</t>
   </si>
   <si>
@@ -130,30 +106,18 @@
     <t>series_002_2_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.102755089973625799055786462646268820450/series_002_2_CR/A2504257770 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>30c4fa7850e9f72b72e3880fd309db5b</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.102755089973625799055786462646268820450/series_002_2_CR/A2504257770 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>f3d21293d38d141635d133f4c463c534</t>
   </si>
   <si>
     <t>2.25.102965897799404973225419898683246248872</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.102965897799404973225419898683246248872/series_001_2_CR/A250726353 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>c46fa0abd355f6f46a425ea1390573db</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.102965897799404973225419898683246248872/series_001_2_CR/A250726353 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>182012b381449d23372e5b34377c091c</t>
   </si>
   <si>
@@ -163,60 +127,36 @@
     <t>series_001_3_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.103868781101960771917584077315578649178/series_001_3_CR/A2507485409 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>436427ad008ead62368f6d6b594a0ec6</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.103868781101960771917584077315578649178/series_001_3_CR/A2507485409 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>ba552827f4befd82290a55038dcb2822</t>
   </si>
   <si>
     <t>2.25.105033841136787477881326326053319223817</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.105033841136787477881326326053319223817/series_001_2_CR/A250790559 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>303535a3498b11e240f613d13eb194b7</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.105033841136787477881326326053319223817/series_001_2_CR/A250790559 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>e2e22d7218b2180df44febd12628e0e3</t>
   </si>
   <si>
     <t>2.25.11175860580562939441493697221497597640</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.11175860580562939441493697221497597640/series_003_2_CR/A2507431060 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>0f52068c243c4aebf95c99db45295ae7</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.11175860580562939441493697221497597640/series_003_2_CR/A2507431060 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>8368ecee695c64b55f323e9e20c11d87</t>
   </si>
   <si>
     <t>2.25.114887542067602662452692698814728642117</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.114887542067602662452692698814728642117/series_001_2_CR/A2504131887 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>5dd7cf35bb63465d35e4869fc48beef3</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.114887542067602662452692698814728642117/series_001_2_CR/A2504131887 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>235539cff4e149de325be2425b353b81</t>
   </si>
   <si>
@@ -226,45 +166,27 @@
     <t>2.25.116822802042655971810859435524105064465</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.116822802042655971810859435524105064465/series_003_2_CR/A2507273296 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>7ea57f17aca2aad099ecfc4b06572c61</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.116822802042655971810859435524105064465/series_003_2_CR/A2507273296 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>fcc765c39ac3d6b0c8f3a03428ea9ea3</t>
   </si>
   <si>
     <t>2.25.122446767306607067205618235949445789306</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.122446767306607067205618235949445789306/series_001_2_CR/A2504255080 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>7f49ebfcd4f836d8df9b35ba05c2be41</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.122446767306607067205618235949445789306/series_001_2_CR/A2504255080 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>833e01e9eac64a0aa79c503e78d24466</t>
   </si>
   <si>
     <t>2.25.124890633326693921702195356152595253940</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.124890633326693921702195356152595253940/series_002_2_CR/A2504263153 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>7635b566378143615ac129d4c9f8fe04</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.124890633326693921702195356152595253940/series_002_2_CR/A2504263153 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>02c8e9c29438e2ea0092b6050839defd</t>
   </si>
   <si>
@@ -274,291 +196,177 @@
     <t>series_002_3_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.126293418391331346694592071563510265596/series_002_3_CR/A2507250865 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>17c27fc5ea2dbfe95c7949fe607ccf79</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.126293418391331346694592071563510265596/series_002_3_CR/A2507250865 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>d90d61c9a1e9482c3ad8017f139fc0e8</t>
   </si>
   <si>
     <t>2.25.127126130998341190348103034690069487890</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.127126130998341190348103034690069487890/series_002_2_CR/A250428736 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>97cac68ceaeaa93a35e30c3c0211a3e6</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.127126130998341190348103034690069487890/series_002_2_CR/A250428736 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>137c2b1171f8abe1a17d88c14d2b5f14</t>
   </si>
   <si>
     <t>2.25.12798473087614376830819854616447908612</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.12798473087614376830819854616447908612/series_002_2_CR/A2507538847 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>b943ec201aa17ab9526322ec8daaa658</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.12798473087614376830819854616447908612/series_002_2_CR/A2507538847 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>8208800f6d71382513e12f74650d5901</t>
   </si>
   <si>
     <t>2.25.128990540359421489042453547244535073735</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.128990540359421489042453547244535073735/series_002_2_CR/A2507388698 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>ba32d92c18ac2770e2a963b5c4cd1149</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.128990540359421489042453547244535073735/series_002_2_CR/A2507388698 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>beea79b038ddf85a0b5b70c0ecb690b6</t>
   </si>
   <si>
     <t>2.25.129239680100193368599713239115902740628</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.129239680100193368599713239115902740628/series_003_3_CR/A250757345 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>4e4eaa7980f08d07d6042e2bbfa20c4f</t>
   </si>
   <si>
     <t>2.25.13069823278093578548407087310307113784</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13069823278093578548407087310307113784/series_003_2_CR/A2507242667 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>fc7b38cff6f8953544f1b6ec6f91fcd2</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13069823278093578548407087310307113784/series_003_2_CR/A2507242667 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>f5f4f322933a672be70e536d6ff1083e</t>
   </si>
   <si>
     <t>2.25.132083163398091874662674590622589534350</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.132083163398091874662674590622589534350/series_003_2_CR/A2507386583 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>c2f8e2599ec7baede0534faf8c3a6686</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.132083163398091874662674590622589534350/series_003_2_CR/A2507386583 DXA Exam/CR DXA Images/CR000002.dcm</t>
-  </si>
-  <si>
     <t>0b8dd276c02d92a89a06c2f08321b1ef</t>
   </si>
   <si>
     <t>2.25.132272637351979990811754009849547633391</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.132272637351979990811754009849547633391/series_003_3_CR/A2504141080 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>b1abf8005764529b10a817d85c814441</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.132272637351979990811754009849547633391/series_003_3_CR/A2504141080 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>e700b0b930e3972e205480f6e731aa93</t>
   </si>
   <si>
     <t>2.25.13325817932854000792938662637654885530</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13325817932854000792938662637654885530/series_002_2_CR/A2507365486 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>96e6698d4179f3eade7e3237302a0647</t>
   </si>
   <si>
     <t>CR000005.dcm</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13325817932854000792938662637654885530/series_002_2_CR/A2507365486 DXA/CR DXA/CR000005.dcm</t>
-  </si>
-  <si>
     <t>02ec26d7516752e33d0389fa6c06f87f</t>
   </si>
   <si>
     <t>2.25.134456506307367483341018281460841912845</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.134456506307367483341018281460841912845/series_002_2_CR/A2507120612 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>8b4a350e651cc215d179d9fe716f6c61</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.134456506307367483341018281460841912845/series_002_2_CR/A2507120612 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>63a2450aa476f55f17651a5c7de5ba16</t>
   </si>
   <si>
     <t>2.25.135241889065705954191821710363605596815</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.135241889065705954191821710363605596815/series_003_3_CR/A250715060 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>39fabec0c166e6637ef86479bff5a486</t>
   </si>
   <si>
     <t>2.25.137344827330550141320158285144101816664</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.137344827330550141320158285144101816664/series_003_3_CR/A2507146630 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>32e171e2afe497ecd1df5d56301c2c02</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.137344827330550141320158285144101816664/series_003_3_CR/A2507146630 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>ebeb7b6e13e099bc827567d7332054cc</t>
   </si>
   <si>
     <t>2.25.13983650679559142983913935144968795415</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13983650679559142983913935144968795415/series_003_2_CR/A2504335111 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>65070df633abd52677506642265acf30</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.13983650679559142983913935144968795415/series_003_2_CR/A2504335111 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>a5160bbe50eed8140d6ead84a22a0f17</t>
   </si>
   <si>
     <t>2.25.144941557565802351596730914409170713112</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.144941557565802351596730914409170713112/series_001_2_CR/A250728979 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>53cef334bccff633f11a55b867715111</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.144941557565802351596730914409170713112/series_001_2_CR/A250728979 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>7c541138e14219b66ce9ae5ea32f365f</t>
   </si>
   <si>
     <t>2.25.145848300160680194368420189079847088556</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.145848300160680194368420189079847088556/series_002_2_CR/A2504248615 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>767378168ec1acd2d7860cad99d759b6</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.145848300160680194368420189079847088556/series_002_2_CR/A2504248615 DXA Exam/CR DXA Images/CR000001.dcm</t>
-  </si>
-  <si>
     <t>40c9f868654edec48d235a9c6eadeee6</t>
   </si>
   <si>
     <t>2.25.151186844055172005615813066162721550889</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.151186844055172005615813066162721550889/series_002_2_CR/A250436130 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>b7bcd7a0209a99779e6ae584d5609559</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.151186844055172005615813066162721550889/series_002_2_CR/A250436130 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>7de8ea0896c43a92e481c0e0b9d9f468</t>
   </si>
   <si>
     <t>2.25.156021661584944120526934974594604520993</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156021661584944120526934974594604520993/series_003_2_CR/A2507142228 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>5e1beebe4da1a049ef57c76241a72083</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156021661584944120526934974594604520993/series_003_2_CR/A2507142228 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>10cdfafb016c3d46b3a6332f0bbfcf56</t>
   </si>
   <si>
     <t>2.25.156375884487675936513403083218009333856</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156375884487675936513403083218009333856/series_003_2_CR/A250727121 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>4cf51af9530559be5ef19c7549f04b83</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156375884487675936513403083218009333856/series_003_2_CR/A250727121 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>8e136f1c7019b3692d4d457c59212483</t>
   </si>
   <si>
     <t>2.25.156389075510671877606923458507011517218</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156389075510671877606923458507011517218/series_001_2_CR/A2507389755 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>5ef1b015077fa74fe7afbfa91ef3ecad</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.156389075510671877606923458507011517218/series_001_2_CR/A2507389755 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>3a3fd4544e820271d2bc7eff70eeae29</t>
   </si>
   <si>
     <t>2.25.157462338378550185821790046400986801350</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.157462338378550185821790046400986801350/series_001_2_CR/A2507498707 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>7fb0901026cdefa43fca7ea48f2355c7</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.157462338378550185821790046400986801350/series_001_2_CR/A2507498707 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>f8af64e8ac274a096f7c6cdb3e26974f</t>
   </si>
   <si>
@@ -568,69 +376,42 @@
     <t>series_003_6_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.158646777318759504110695916200521633609/series_003_6_CR/A2507266260 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>f7b5dd7222a6221e8d24a1522f6564bc</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.158646777318759504110695916200521633609/series_003_6_CR/A2507266260 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>b8d6bf2a4368b5c59d6b78a26aa12691</t>
   </si>
   <si>
     <t>2.25.164566280810634620154538016595892212884</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.164566280810634620154538016595892212884/series_001_2_CR/A2504291878 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>c78c070a09d513a26cf533d290d9dd3a</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.164566280810634620154538016595892212884/series_001_2_CR/A2504291878 DXA Exam/CR DXA Images/CR000002.dcm</t>
-  </si>
-  <si>
     <t>c04b6479d6ea05e97e0852b76e8fb94f</t>
   </si>
   <si>
     <t>2.25.165091430504580219034019815337441064349</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.165091430504580219034019815337441064349/series_001_2_CR/A2504415443 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>151be2dad8a644b84dd14be92d00caf6</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.165091430504580219034019815337441064349/series_001_2_CR/A2504415443 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>29cf28b96c1f722ede3dcfaf746a68d2</t>
   </si>
   <si>
     <t>2.25.165355673991587715046346525964554729786</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.165355673991587715046346525964554729786/series_003_3_CR/A2506448267 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>6d06e4b4ba594657589dfe59938d4640</t>
   </si>
   <si>
     <t>2.25.167344201679287285499405412654740659745</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.167344201679287285499405412654740659745/series_003_2_CR/A2504249537 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>30627c679776763b27e9ec8485b59b22</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.167344201679287285499405412654740659745/series_003_2_CR/A2504249537 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>79f5feddd748ab50f4b82a954e88789d</t>
   </si>
   <si>
@@ -640,607 +421,826 @@
     <t>series_004_2_CR</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.16773626720107440979805052259711419763/series_004_2_CR/A2507537392 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>b55961cc249a48438df7aafd86a15085</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.16773626720107440979805052259711419763/series_004_2_CR/A2507537392 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>7f9bb98e52e32e5fb2ec905982dab423</t>
   </si>
   <si>
     <t>2.25.168317503020329569414190677927680518621</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.168317503020329569414190677927680518621/series_004_2_CR/A2507557128 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>0e37cfbd6f87c73bf8528b50918c5ca9</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.168317503020329569414190677927680518621/series_004_2_CR/A2507557128 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>84215eaf271a6ede1b69011e05209904</t>
   </si>
   <si>
     <t>2.25.172445998420765569384934552191547932566</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.172445998420765569384934552191547932566/series_004_2_CR/A2507368766 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>af16a958c221cdee48fee2153ad94a68</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.172445998420765569384934552191547932566/series_004_2_CR/A2507368766 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>9065273c082a78c6144aa27beb433d6d</t>
   </si>
   <si>
     <t>2.25.173731186748227489808861376513577450951</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.173731186748227489808861376513577450951/series_002_2_CR/A2507188958 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>3459487b72e11185a4f01a2cb361724b</t>
   </si>
   <si>
     <t>2.25.173753313169335820519632380691065649420</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.173753313169335820519632380691065649420/series_003_2_CR/A2504265499 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>72eb12218898fa7a50d02dd1b44bf4da</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.173753313169335820519632380691065649420/series_003_2_CR/A2504265499 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>b89fb123b7e85b41dc13aea205c8b922</t>
   </si>
   <si>
     <t>2.25.175881661753775295785039265792986971602</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.175881661753775295785039265792986971602/series_003_2_CR/A2507266462 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>d2728574df7b16469b4cf6703dcec819</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.175881661753775295785039265792986971602/series_003_2_CR/A2507266462 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>5789c34e0078a33974b4b47fef0918d5</t>
   </si>
   <si>
     <t>2.25.175903805423871105435148927871625232853</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.175903805423871105435148927871625232853/series_001_2_CR/A2507159447 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>0544b7ba571305566097a5bc953a09a4</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.175903805423871105435148927871625232853/series_001_2_CR/A2507159447 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>59998e2c86d62cd9b96340d11d191a42</t>
   </si>
   <si>
     <t>2.25.17706555930735581384953296958427669848</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.17706555930735581384953296958427669848/series_004_3_CR/A2504146513 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>5a1bf715e1633dadeab6b98a83d5ad9f</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.17706555930735581384953296958427669848/series_004_3_CR/A2504146513 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>5f36cb4d72d3b7846f1ac67ac2a6d5a5</t>
   </si>
   <si>
     <t>2.25.177745077805190810016231350557005569203</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.177745077805190810016231350557005569203/series_002_2_CR/A2504273759 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>3aa3f9f9fcf557b06d7eb970c93a8c11</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.177745077805190810016231350557005569203/series_002_2_CR/A2504273759 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>54256f2d0267330bd1d8904a59ffffb6</t>
   </si>
   <si>
     <t>2.25.181196659018348153828200695057897449628</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.181196659018348153828200695057897449628/series_004_2_CR/A2507370620 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>515df3f5a450ec634198c8e496f5b6bf</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.181196659018348153828200695057897449628/series_004_2_CR/A2507370620 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>63e925a5a8d6827e86075c486f64d359</t>
   </si>
   <si>
     <t>2.25.184198356665635336833172191504278054074</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.184198356665635336833172191504278054074/series_004_2_CR/A250788286 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>65d7e7cdee9146a60e00c99d8382c1e3</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.184198356665635336833172191504278054074/series_004_2_CR/A250788286 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>f1fcc7d52cf47fd30550745b7952349f</t>
   </si>
   <si>
     <t>2.25.186201010600484120326273381077449377115</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.186201010600484120326273381077449377115/series_004_2_CR/A250777475 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>86139d1b0fe57b7d03f0f96d0fc6ae67</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.186201010600484120326273381077449377115/series_004_2_CR/A250777475 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>ef7f7715838202032a1c148d89d480c1</t>
   </si>
   <si>
     <t>2.25.190331309633057244929837507901317950031</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.190331309633057244929837507901317950031/series_001_2_CR/A250791815 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>2e00afac2f6f1e37096c1abb94580e50</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.190331309633057244929837507901317950031/series_001_2_CR/A250791815 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>8673da062a76fc3fcbcda7b85ed8f009</t>
   </si>
   <si>
     <t>2.25.190807933410234695931591553323782771995</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.190807933410234695931591553323782771995/series_002_3_CR/A250762254 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>71f3f7e22be7f6952a193045a1bc2227</t>
   </si>
   <si>
     <t>2.25.215177279960644564778148238928738915103</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.215177279960644564778148238928738915103/series_002_2_CR/A2504147013 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>a43d18ce7764ea554cf29dce162b2e20</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.215177279960644564778148238928738915103/series_002_2_CR/A2504147013 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>2dff71d9a86f271e32d901d6dcc0dd0a</t>
   </si>
   <si>
     <t>2.25.217397325224876728316360420804118329081</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.217397325224876728316360420804118329081/series_002_2_CR/A250474631 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>1f3bd3dee17cfed65d38c5a232bb6b81</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.217397325224876728316360420804118329081/series_002_2_CR/A250474631 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>67a8280afe381d61df32a82578bb62e0</t>
   </si>
   <si>
     <t>2.25.234651502352368356456298825489565282446</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.234651502352368356456298825489565282446/series_002_2_CR/A2504307193 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>0f4bebf1caad4e92ec95e79f95879486</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.234651502352368356456298825489565282446/series_002_2_CR/A2504307193 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>924764394acca874a843bc6febdca372</t>
   </si>
   <si>
     <t>2.25.247714038039430659432048101646401574824</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.247714038039430659432048101646401574824/series_002_2_CR/A2504238024 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>99f9ec75177bc5fe95d531951ed6ddf9</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.247714038039430659432048101646401574824/series_002_2_CR/A2504238024 DXA Exam/CR DXA Images/CR000001.dcm</t>
-  </si>
-  <si>
     <t>e7479e61dfdac67493bd430e61f96f84</t>
   </si>
   <si>
     <t>2.25.269648774413746842548908998641183395622</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.269648774413746842548908998641183395622/series_001_2_CR/A2504393664 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>f053dc8315a23e9c5b46c186ba5acd33</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.269648774413746842548908998641183395622/series_001_2_CR/A2504393664 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>0ac9ed6eb0a06e7d9474ba6f92820142</t>
   </si>
   <si>
     <t>2.25.272690031744216183651627058502316132741</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.272690031744216183651627058502316132741/series_002_2_CR/A2504373414 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>1ed7dccce1d27980dea1622726d3c65e</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.272690031744216183651627058502316132741/series_002_2_CR/A2504373414 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>62f98a0d532f817a78b27b79e4a84153</t>
   </si>
   <si>
     <t>2.25.276415754443998872860614500027519740375</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.276415754443998872860614500027519740375/series_002_2_CR/A2504387089 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>0d6eee2f3b32c866a63c33d3972d1bca</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.276415754443998872860614500027519740375/series_002_2_CR/A2504387089 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>877cb0e1f382ee0509565d171bb73799</t>
   </si>
   <si>
     <t>2.25.277752758923974029595977676354128739670</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.277752758923974029595977676354128739670/series_002_2_CR/A2504223752 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>0d0c6ec994e4d046f2a0fe0908c6af5d</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.277752758923974029595977676354128739670/series_002_2_CR/A2504223752 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>ed070638f923b1a07ea1e32bb61cafcc</t>
   </si>
   <si>
     <t>2.25.286999464611662854355201599068538813496</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.286999464611662854355201599068538813496/series_003_2_CR/A2504223477 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>0437d6b17ea83ad292aca806ce357016</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.286999464611662854355201599068538813496/series_003_2_CR/A2504223477 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>c73229c19153bf3e9fe617f7afcb95c3</t>
   </si>
   <si>
     <t>2.25.29638026465755240167985424461715024381</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.29638026465755240167985424461715024381/series_004_3_CR/A2504115579 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>87e563f0b04b2e7f1b96bdfcdd6d1918</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.29638026465755240167985424461715024381/series_004_3_CR/A2504115579 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>3544f1e25db9282af42586435c9db935</t>
   </si>
   <si>
     <t>2.25.307021710202910067378603383388989711646</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.307021710202910067378603383388989711646/series_004_2_CR/A2504110565 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>3434c1bd4b3c91609db0e03a661947bb</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.307021710202910067378603383388989711646/series_004_2_CR/A2504110565 DXA/CR DXA/CR000004.dcm</t>
-  </si>
-  <si>
     <t>d2d11770ad55e01940d001ca5b0acb50</t>
   </si>
   <si>
     <t>2.25.309085571913348252136520206003694446566</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.309085571913348252136520206003694446566/series_002_2_CR/A2504116267 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>65a4522dcb1791651cb2f1bcb5d18400</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.309085571913348252136520206003694446566/series_002_2_CR/A2504116267 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>b97ec0a3d7346abaf047424070f8b5f2</t>
   </si>
   <si>
     <t>2.25.314147167453134440746270747484612743945</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.314147167453134440746270747484612743945/series_002_2_CR/A2504224780 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>b11e0f5528c3a8361643a8704c6fbc6c</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.314147167453134440746270747484612743945/series_002_2_CR/A2504224780 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>0d1167d443f96f04fbd20e8999e746bd</t>
   </si>
   <si>
     <t>2.25.339027809107632348165171236474821772940</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.339027809107632348165171236474821772940/series_001_2_CR/A2504349642 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>828539fdd64d02ae3540161703504c10</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.339027809107632348165171236474821772940/series_001_2_CR/A2504349642 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>11370be60a33e4e0d1584960d55b54ff</t>
   </si>
   <si>
     <t>2.25.340839477910528898406207279980417945</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.340839477910528898406207279980417945/series_001_2_CR/A2504224555 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>b8031b81c396bcbe86a37c69e8febec6</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.340839477910528898406207279980417945/series_001_2_CR/A2504224555 DXA Exam/CR DXA Images/CR000001.dcm</t>
-  </si>
-  <si>
     <t>34f81fb821f863ec648ee0ee0129dffb</t>
   </si>
   <si>
     <t>2.25.37515662379281069436632838996073181551</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.37515662379281069436632838996073181551/series_001_2_CR/A2504329840 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>bb0c19681ee1a246f1469a27bcf698b3</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.37515662379281069436632838996073181551/series_001_2_CR/A2504329840 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>d64326eb987049b500bed9457ed1e2c9</t>
   </si>
   <si>
     <t>2.25.39068163399801173920284179500049527111</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.39068163399801173920284179500049527111/series_002_2_CR/A2504195842 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>cb2208eacd0eb2510e2b54ebc65727dc</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.39068163399801173920284179500049527111/series_002_2_CR/A2504195842 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>d805e813a522b56a9d54ab1217b9b8d2</t>
   </si>
   <si>
     <t>2.25.48906424954135283790354958243772558962</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.48906424954135283790354958243772558962/series_001_2_CR/A2504185596 DXA Exam/CR DXA Images/CR000000.dcm</t>
-  </si>
-  <si>
     <t>5a791c941d7d2794b886cec0d19220a7</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.48906424954135283790354958243772558962/series_001_2_CR/A2504185596 DXA Exam/CR DXA Images/CR000001.dcm</t>
-  </si>
-  <si>
     <t>35b77a2b85f154a6e8ec0cf6db13a404</t>
   </si>
   <si>
     <t>2.25.52982400970721161435951723390541696819</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.52982400970721161435951723390541696819/series_001_2_CR/A2504331065 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>6e8e250a82fe25963942aafddaf6848a</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.52982400970721161435951723390541696819/series_001_2_CR/A2504331065 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>0f019928163fad12df1c975a3e509883</t>
   </si>
   <si>
     <t>2.25.65954778282254353457041255543338557112</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.65954778282254353457041255543338557112/series_004_3_CR/A2504246289 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>6d32b59f92dcb2202564a3602f3f9bbb</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.65954778282254353457041255543338557112/series_004_3_CR/A2504246289 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>4d1342777300b7e72265d36ea4fd1610</t>
   </si>
   <si>
     <t>2.25.66397484472966116002950503539482860450</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.66397484472966116002950503539482860450/series_001_2_CR/A2504194637 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>7d045311e7eb6a179ead4c84e14b22d7</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.66397484472966116002950503539482860450/series_001_2_CR/A2504194637 DXA/CR DXA/CR000003.dcm</t>
-  </si>
-  <si>
     <t>5a4de68533c7650e11d7c7d30eac676f</t>
   </si>
   <si>
     <t>2.25.73070100851377917031356937075051545239</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.73070100851377917031356937075051545239/series_002_2_CR/A2504239110 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>9e942cc0f0778ad38883b84f4d3b1944</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.73070100851377917031356937075051545239/series_002_2_CR/A2504239110 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>a32b3abc0a4efbb967983f4a479deee4</t>
   </si>
   <si>
     <t>2.25.76710355977373089612172037086913478687</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.76710355977373089612172037086913478687/series_002_3_CR/A2504104830 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>51c7f2e87c6d4e74a0001ecf3cba812a</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.76710355977373089612172037086913478687/series_002_3_CR/A2504104830 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>7dc31371530544ce58b8511af00139d9</t>
   </si>
   <si>
     <t>2.25.78999454687125053757525542837745968726</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.78999454687125053757525542837745968726/series_004_3_CR/A2504222617 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>d6a2efe4ec22f66f58d8f4e455ff4009</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.78999454687125053757525542837745968726/series_004_3_CR/A2504222617 DXA/CR DXA/CR000001.dcm</t>
-  </si>
-  <si>
     <t>edc92f3c6301717d986e4c3a8bb55102</t>
   </si>
   <si>
     <t>2.25.82912555346523716720160717883917565880</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.82912555346523716720160717883917565880/series_002_2_CR/A2504149480 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>7aaee5f96a3ea8d4e49092579fa4cf28</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.82912555346523716720160717883917565880/series_002_2_CR/A2504149480 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>99181f92d61399f19326fd6ac30a78f3</t>
   </si>
   <si>
     <t>2.25.87869906212286587478854831452123526595</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.87869906212286587478854831452123526595/series_002_2_CR/A250419699 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>5e284ad84b50e21e704ca615e70b5213</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.87869906212286587478854831452123526595/series_002_2_CR/A250419699 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>802e0189372f2f46ad4a1d3dc6d29e2e</t>
   </si>
   <si>
     <t>2.25.91981043841368764114007975581101713077</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.91981043841368764114007975581101713077/series_003_2_CR/A250496619 DXA/CR DXA/CR000000.dcm</t>
-  </si>
-  <si>
     <t>03a4ef8d87f71d9e8e507cbf14c89bbe</t>
   </si>
   <si>
-    <t>НД_для_обучения/Исследования/2.25.91981043841368764114007975581101713077/series_003_2_CR/A250496619 DXA/CR DXA/CR000002.dcm</t>
-  </si>
-  <si>
     <t>4ee9ef8155ff487a0618b3e8f8603f82</t>
   </si>
   <si>
     <t>position_defects</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250403090444/series_004_3_CR/DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250403090444/series_004_3_CR/DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250403092052/series_003_3_CR/DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250403092052/series_003_3_CR/DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250407113211/series_001_2_CR/DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/1.2.840.113619.2.110.512719.20250407113211/series_001_2_CR/DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.10245777060263212829333021434108890537/series_003_2_CR/A2504412435 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.10245777060263212829333021434108890537/series_003_2_CR/A2504412435 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.102755089973625799055786462646268820450/series_002_2_CR/A2504257770 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.102755089973625799055786462646268820450/series_002_2_CR/A2504257770 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.102965897799404973225419898683246248872/series_001_2_CR/A250726353 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.102965897799404973225419898683246248872/series_001_2_CR/A250726353 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.103868781101960771917584077315578649178/series_001_3_CR/A2507485409 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.103868781101960771917584077315578649178/series_001_3_CR/A2507485409 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.105033841136787477881326326053319223817/series_001_2_CR/A250790559 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.105033841136787477881326326053319223817/series_001_2_CR/A250790559 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.11175860580562939441493697221497597640/series_003_2_CR/A2507431060 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.11175860580562939441493697221497597640/series_003_2_CR/A2507431060 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.114887542067602662452692698814728642117/series_001_2_CR/A2504131887 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.114887542067602662452692698814728642117/series_001_2_CR/A2504131887 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.116822802042655971810859435524105064465/series_003_2_CR/A2507273296 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.116822802042655971810859435524105064465/series_003_2_CR/A2507273296 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.122446767306607067205618235949445789306/series_001_2_CR/A2504255080 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.122446767306607067205618235949445789306/series_001_2_CR/A2504255080 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.124890633326693921702195356152595253940/series_002_2_CR/A2504263153 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.124890633326693921702195356152595253940/series_002_2_CR/A2504263153 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.126293418391331346694592071563510265596/series_002_3_CR/A2507250865 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.126293418391331346694592071563510265596/series_002_3_CR/A2507250865 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.127126130998341190348103034690069487890/series_002_2_CR/A250428736 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.127126130998341190348103034690069487890/series_002_2_CR/A250428736 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.12798473087614376830819854616447908612/series_002_2_CR/A2507538847 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.12798473087614376830819854616447908612/series_002_2_CR/A2507538847 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.128990540359421489042453547244535073735/series_002_2_CR/A2507388698 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.128990540359421489042453547244535073735/series_002_2_CR/A2507388698 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.129239680100193368599713239115902740628/series_003_3_CR/A250757345 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13069823278093578548407087310307113784/series_003_2_CR/A2507242667 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13069823278093578548407087310307113784/series_003_2_CR/A2507242667 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.132083163398091874662674590622589534350/series_003_2_CR/A2507386583 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.132083163398091874662674590622589534350/series_003_2_CR/A2507386583 DXA Exam/CR DXA Images/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.132272637351979990811754009849547633391/series_003_3_CR/A2504141080 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.132272637351979990811754009849547633391/series_003_3_CR/A2504141080 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13325817932854000792938662637654885530/series_002_2_CR/A2507365486 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13325817932854000792938662637654885530/series_002_2_CR/A2507365486 DXA/CR DXA/CR000005.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.134456506307367483341018281460841912845/series_002_2_CR/A2507120612 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.134456506307367483341018281460841912845/series_002_2_CR/A2507120612 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.135241889065705954191821710363605596815/series_003_3_CR/A250715060 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.137344827330550141320158285144101816664/series_003_3_CR/A2507146630 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.137344827330550141320158285144101816664/series_003_3_CR/A2507146630 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13983650679559142983913935144968795415/series_003_2_CR/A2504335111 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.13983650679559142983913935144968795415/series_003_2_CR/A2504335111 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.144941557565802351596730914409170713112/series_001_2_CR/A250728979 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.144941557565802351596730914409170713112/series_001_2_CR/A250728979 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.145848300160680194368420189079847088556/series_002_2_CR/A2504248615 DXA Exam/CR DXA Images/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.145848300160680194368420189079847088556/series_002_2_CR/A2504248615 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.151186844055172005615813066162721550889/series_002_2_CR/A250436130 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.151186844055172005615813066162721550889/series_002_2_CR/A250436130 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156021661584944120526934974594604520993/series_003_2_CR/A2507142228 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156021661584944120526934974594604520993/series_003_2_CR/A2507142228 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156375884487675936513403083218009333856/series_003_2_CR/A250727121 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156375884487675936513403083218009333856/series_003_2_CR/A250727121 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156389075510671877606923458507011517218/series_001_2_CR/A2507389755 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.156389075510671877606923458507011517218/series_001_2_CR/A2507389755 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.157462338378550185821790046400986801350/series_001_2_CR/A2507498707 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.157462338378550185821790046400986801350/series_001_2_CR/A2507498707 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.158646777318759504110695916200521633609/series_003_6_CR/A2507266260 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.158646777318759504110695916200521633609/series_003_6_CR/A2507266260 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.164566280810634620154538016595892212884/series_001_2_CR/A2504291878 DXA Exam/CR DXA Images/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.164566280810634620154538016595892212884/series_001_2_CR/A2504291878 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.165091430504580219034019815337441064349/series_001_2_CR/A2504415443 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.165091430504580219034019815337441064349/series_001_2_CR/A2504415443 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.165355673991587715046346525964554729786/series_003_3_CR/A2506448267 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.167344201679287285499405412654740659745/series_003_2_CR/A2504249537 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.167344201679287285499405412654740659745/series_003_2_CR/A2504249537 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.16773626720107440979805052259711419763/series_004_2_CR/A2507537392 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.16773626720107440979805052259711419763/series_004_2_CR/A2507537392 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.168317503020329569414190677927680518621/series_004_2_CR/A2507557128 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.168317503020329569414190677927680518621/series_004_2_CR/A2507557128 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.172445998420765569384934552191547932566/series_004_2_CR/A2507368766 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.172445998420765569384934552191547932566/series_004_2_CR/A2507368766 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.173731186748227489808861376513577450951/series_002_2_CR/A2507188958 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.173753313169335820519632380691065649420/series_003_2_CR/A2504265499 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.173753313169335820519632380691065649420/series_003_2_CR/A2504265499 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.175881661753775295785039265792986971602/series_003_2_CR/A2507266462 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.175881661753775295785039265792986971602/series_003_2_CR/A2507266462 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.175903805423871105435148927871625232853/series_001_2_CR/A2507159447 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.175903805423871105435148927871625232853/series_001_2_CR/A2507159447 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.17706555930735581384953296958427669848/series_004_3_CR/A2504146513 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.17706555930735581384953296958427669848/series_004_3_CR/A2504146513 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.177745077805190810016231350557005569203/series_002_2_CR/A2504273759 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.177745077805190810016231350557005569203/series_002_2_CR/A2504273759 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.181196659018348153828200695057897449628/series_004_2_CR/A2507370620 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.181196659018348153828200695057897449628/series_004_2_CR/A2507370620 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.184198356665635336833172191504278054074/series_004_2_CR/A250788286 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.184198356665635336833172191504278054074/series_004_2_CR/A250788286 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.186201010600484120326273381077449377115/series_004_2_CR/A250777475 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.186201010600484120326273381077449377115/series_004_2_CR/A250777475 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.190331309633057244929837507901317950031/series_001_2_CR/A250791815 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.190331309633057244929837507901317950031/series_001_2_CR/A250791815 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.190807933410234695931591553323782771995/series_002_3_CR/A250762254 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.215177279960644564778148238928738915103/series_002_2_CR/A2504147013 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.215177279960644564778148238928738915103/series_002_2_CR/A2504147013 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.217397325224876728316360420804118329081/series_002_2_CR/A250474631 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.217397325224876728316360420804118329081/series_002_2_CR/A250474631 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.234651502352368356456298825489565282446/series_002_2_CR/A2504307193 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.234651502352368356456298825489565282446/series_002_2_CR/A2504307193 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.247714038039430659432048101646401574824/series_002_2_CR/A2504238024 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.247714038039430659432048101646401574824/series_002_2_CR/A2504238024 DXA Exam/CR DXA Images/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.269648774413746842548908998641183395622/series_001_2_CR/A2504393664 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.269648774413746842548908998641183395622/series_001_2_CR/A2504393664 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.272690031744216183651627058502316132741/series_002_2_CR/A2504373414 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.272690031744216183651627058502316132741/series_002_2_CR/A2504373414 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.276415754443998872860614500027519740375/series_002_2_CR/A2504387089 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.276415754443998872860614500027519740375/series_002_2_CR/A2504387089 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.277752758923974029595977676354128739670/series_002_2_CR/A2504223752 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.277752758923974029595977676354128739670/series_002_2_CR/A2504223752 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.286999464611662854355201599068538813496/series_003_2_CR/A2504223477 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.286999464611662854355201599068538813496/series_003_2_CR/A2504223477 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.29638026465755240167985424461715024381/series_004_3_CR/A2504115579 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.29638026465755240167985424461715024381/series_004_3_CR/A2504115579 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.307021710202910067378603383388989711646/series_004_2_CR/A2504110565 DXA/CR DXA/CR000004.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.307021710202910067378603383388989711646/series_004_2_CR/A2504110565 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.309085571913348252136520206003694446566/series_002_2_CR/A2504116267 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.309085571913348252136520206003694446566/series_002_2_CR/A2504116267 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.314147167453134440746270747484612743945/series_002_2_CR/A2504224780 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.314147167453134440746270747484612743945/series_002_2_CR/A2504224780 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.339027809107632348165171236474821772940/series_001_2_CR/A2504349642 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.339027809107632348165171236474821772940/series_001_2_CR/A2504349642 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.340839477910528898406207279980417945/series_001_2_CR/A2504224555 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.340839477910528898406207279980417945/series_001_2_CR/A2504224555 DXA Exam/CR DXA Images/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.37515662379281069436632838996073181551/series_001_2_CR/A2504329840 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.37515662379281069436632838996073181551/series_001_2_CR/A2504329840 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.39068163399801173920284179500049527111/series_002_2_CR/A2504195842 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.39068163399801173920284179500049527111/series_002_2_CR/A2504195842 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.48906424954135283790354958243772558962/series_001_2_CR/A2504185596 DXA Exam/CR DXA Images/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.48906424954135283790354958243772558962/series_001_2_CR/A2504185596 DXA Exam/CR DXA Images/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.52982400970721161435951723390541696819/series_001_2_CR/A2504331065 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.52982400970721161435951723390541696819/series_001_2_CR/A2504331065 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.65954778282254353457041255543338557112/series_004_3_CR/A2504246289 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.65954778282254353457041255543338557112/series_004_3_CR/A2504246289 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.66397484472966116002950503539482860450/series_001_2_CR/A2504194637 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.66397484472966116002950503539482860450/series_001_2_CR/A2504194637 DXA/CR DXA/CR000003.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.73070100851377917031356937075051545239/series_002_2_CR/A2504239110 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.73070100851377917031356937075051545239/series_002_2_CR/A2504239110 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.76710355977373089612172037086913478687/series_002_3_CR/A2504104830 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.76710355977373089612172037086913478687/series_002_3_CR/A2504104830 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.78999454687125053757525542837745968726/series_004_3_CR/A2504222617 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.78999454687125053757525542837745968726/series_004_3_CR/A2504222617 DXA/CR DXA/CR000001.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.82912555346523716720160717883917565880/series_002_2_CR/A2504149480 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.82912555346523716720160717883917565880/series_002_2_CR/A2504149480 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.87869906212286587478854831452123526595/series_002_2_CR/A250419699 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.87869906212286587478854831452123526595/series_002_2_CR/A250419699 DXA/CR DXA/CR000002.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.91981043841368764114007975581101713077/series_003_2_CR/A250496619 DXA/CR DXA/CR000000.dcm</t>
+  </si>
+  <si>
+    <t>Data/Исследования/2.25.91981043841368764114007975581101713077/series_003_2_CR/A250496619 DXA/CR DXA/CR000002.dcm</t>
   </si>
 </sst>
 </file>
@@ -1586,8 +1586,8 @@
     <col min="1" max="1" width="52.33203125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="18.109375" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="39.109375" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
     <col min="6" max="6" width="14.6640625" customWidth="1"/>
     <col min="7" max="7" width="14.5546875" customWidth="1"/>
     <col min="8" max="8" width="17.77734375" customWidth="1"/>
@@ -1616,7 +1616,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>407</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -1630,10 +1630,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -1653,13 +1653,13 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1673,19 +1673,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1699,19 +1699,19 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
         <v>9</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>259</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1751,19 +1751,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1777,19 +1777,19 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -1803,19 +1803,19 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>262</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1829,19 +1829,19 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>263</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -1855,19 +1855,19 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1881,19 +1881,19 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>265</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1907,19 +1907,19 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>266</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1933,19 +1933,19 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>267</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1959,19 +1959,19 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>268</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1985,19 +1985,19 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>269</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -2011,19 +2011,19 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>270</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2037,19 +2037,19 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>271</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -2063,19 +2063,19 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>272</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2089,19 +2089,19 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>273</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2115,19 +2115,19 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>63</v>
+        <v>274</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
         <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>275</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -2167,19 +2167,19 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -2193,19 +2193,19 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>76</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -2245,19 +2245,19 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -2271,19 +2271,19 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>280</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -2297,19 +2297,19 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -2323,19 +2323,19 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -2349,19 +2349,19 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>283</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -2375,19 +2375,19 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>284</v>
       </c>
       <c r="E31" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -2401,19 +2401,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="E32" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -2427,19 +2427,19 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>286</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -2453,19 +2453,19 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -2479,19 +2479,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D35" t="s">
-        <v>102</v>
+        <v>288</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -2505,19 +2505,19 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>289</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="F36">
         <v>0</v>
@@ -2531,19 +2531,19 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>108</v>
+        <v>290</v>
       </c>
       <c r="E37" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2557,19 +2557,19 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>291</v>
       </c>
       <c r="E38" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -2583,19 +2583,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>113</v>
+        <v>292</v>
       </c>
       <c r="E39" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2609,19 +2609,19 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="E40" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -2635,19 +2635,19 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>294</v>
       </c>
       <c r="E41" t="s">
-        <v>119</v>
+        <v>79</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2661,19 +2661,19 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
         <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="E42" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -2687,19 +2687,19 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
         <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>123</v>
+        <v>296</v>
       </c>
       <c r="E43" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -2713,19 +2713,19 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>297</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -2739,19 +2739,19 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>129</v>
+        <v>298</v>
       </c>
       <c r="E45" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2765,19 +2765,19 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>131</v>
+        <v>299</v>
       </c>
       <c r="E46" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -2791,19 +2791,19 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>300</v>
       </c>
       <c r="E47" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -2817,19 +2817,19 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
         <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>137</v>
+        <v>301</v>
       </c>
       <c r="E48" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2843,19 +2843,19 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="E49" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -2869,19 +2869,19 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>303</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="F50">
         <v>0</v>
@@ -2895,19 +2895,19 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="E51" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -2921,19 +2921,19 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="B52" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>147</v>
+        <v>305</v>
       </c>
       <c r="E52" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2947,19 +2947,19 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>149</v>
+        <v>306</v>
       </c>
       <c r="E53" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -2973,19 +2973,19 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
         <v>10</v>
       </c>
       <c r="D54" t="s">
-        <v>154</v>
+        <v>307</v>
       </c>
       <c r="E54" t="s">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -2999,19 +2999,19 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>308</v>
       </c>
       <c r="E55" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3025,19 +3025,19 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
         <v>10</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="E56" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3051,19 +3051,19 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>159</v>
+        <v>310</v>
       </c>
       <c r="E57" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -3077,19 +3077,19 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="E58" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -3103,19 +3103,19 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>164</v>
+        <v>312</v>
       </c>
       <c r="E59" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -3129,19 +3129,19 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>313</v>
       </c>
       <c r="E60" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -3155,19 +3155,19 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="E61" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -3181,19 +3181,19 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C62" t="s">
         <v>10</v>
       </c>
       <c r="D62" t="s">
-        <v>174</v>
+        <v>315</v>
       </c>
       <c r="E62" t="s">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3207,19 +3207,19 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="E63" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -3233,19 +3233,19 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D64" t="s">
-        <v>179</v>
+        <v>317</v>
       </c>
       <c r="E64" t="s">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3259,19 +3259,19 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>177</v>
+        <v>318</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -3285,19 +3285,19 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="B66" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D66" t="s">
-        <v>185</v>
+        <v>319</v>
       </c>
       <c r="E66" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -3311,19 +3311,19 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>181</v>
+        <v>117</v>
       </c>
       <c r="B67" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>320</v>
       </c>
       <c r="E67" t="s">
-        <v>184</v>
+        <v>119</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -3337,19 +3337,19 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>190</v>
+        <v>321</v>
       </c>
       <c r="E68" t="s">
-        <v>191</v>
+        <v>123</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -3363,19 +3363,19 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>188</v>
+        <v>322</v>
       </c>
       <c r="E69" t="s">
-        <v>189</v>
+        <v>122</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -3389,19 +3389,19 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C70" t="s">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="E70" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -3415,19 +3415,19 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>324</v>
       </c>
       <c r="E71" t="s">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -3441,19 +3441,19 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
       <c r="B72" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>198</v>
+        <v>325</v>
       </c>
       <c r="E72" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3467,19 +3467,19 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>203</v>
+        <v>326</v>
       </c>
       <c r="E73" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -3493,19 +3493,19 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>200</v>
+        <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>201</v>
+        <v>327</v>
       </c>
       <c r="E74" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -3519,19 +3519,19 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="B75" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C75" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D75" t="s">
-        <v>209</v>
+        <v>328</v>
       </c>
       <c r="E75" t="s">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3545,19 +3545,19 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>205</v>
+        <v>132</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C76" t="s">
         <v>10</v>
       </c>
       <c r="D76" t="s">
-        <v>207</v>
+        <v>329</v>
       </c>
       <c r="E76" t="s">
-        <v>208</v>
+        <v>134</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -3571,19 +3571,19 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="B77" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
       </c>
       <c r="D77" t="s">
-        <v>212</v>
+        <v>330</v>
       </c>
       <c r="E77" t="s">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -3597,19 +3597,19 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>211</v>
+        <v>136</v>
       </c>
       <c r="B78" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D78" t="s">
-        <v>214</v>
+        <v>331</v>
       </c>
       <c r="E78" t="s">
-        <v>215</v>
+        <v>138</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -3623,19 +3623,19 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="B79" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="E79" t="s">
-        <v>220</v>
+        <v>141</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3649,19 +3649,19 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C80" t="s">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>217</v>
+        <v>333</v>
       </c>
       <c r="E80" t="s">
-        <v>218</v>
+        <v>140</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -3675,19 +3675,19 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>221</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
         <v>10</v>
       </c>
       <c r="D81" t="s">
-        <v>222</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
-        <v>223</v>
+        <v>143</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -3701,19 +3701,19 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>224</v>
+        <v>144</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D82" t="s">
-        <v>227</v>
+        <v>335</v>
       </c>
       <c r="E82" t="s">
-        <v>228</v>
+        <v>146</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -3727,19 +3727,19 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>224</v>
+        <v>144</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>225</v>
+        <v>336</v>
       </c>
       <c r="E83" t="s">
-        <v>226</v>
+        <v>145</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -3753,19 +3753,19 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>232</v>
+        <v>337</v>
       </c>
       <c r="E84" t="s">
-        <v>233</v>
+        <v>149</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -3779,19 +3779,19 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>229</v>
+        <v>147</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>230</v>
+        <v>338</v>
       </c>
       <c r="E85" t="s">
-        <v>231</v>
+        <v>148</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -3805,19 +3805,19 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D86" t="s">
-        <v>237</v>
+        <v>339</v>
       </c>
       <c r="E86" t="s">
-        <v>238</v>
+        <v>152</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -3831,19 +3831,19 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>234</v>
+        <v>150</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C87" t="s">
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="E87" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="B88" t="s">
         <v>8</v>
@@ -3866,10 +3866,10 @@
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="E88" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -3883,19 +3883,19 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>239</v>
+        <v>153</v>
       </c>
       <c r="B89" t="s">
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D89" t="s">
-        <v>242</v>
+        <v>342</v>
       </c>
       <c r="E89" t="s">
-        <v>243</v>
+        <v>155</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -3909,19 +3909,19 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="B90" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
         <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="E90" t="s">
-        <v>246</v>
+        <v>157</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -3935,19 +3935,19 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>244</v>
+        <v>156</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D91" t="s">
-        <v>247</v>
+        <v>344</v>
       </c>
       <c r="E91" t="s">
-        <v>248</v>
+        <v>158</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -3961,19 +3961,19 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="E92" t="s">
-        <v>251</v>
+        <v>160</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -3987,19 +3987,19 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>249</v>
+        <v>159</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
       </c>
       <c r="D93" t="s">
-        <v>252</v>
+        <v>346</v>
       </c>
       <c r="E93" t="s">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -4013,19 +4013,19 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C94" t="s">
         <v>10</v>
       </c>
       <c r="D94" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="E94" t="s">
-        <v>256</v>
+        <v>163</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4039,19 +4039,19 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>254</v>
+        <v>162</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D95" t="s">
-        <v>257</v>
+        <v>348</v>
       </c>
       <c r="E95" t="s">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -4065,19 +4065,19 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>260</v>
+        <v>349</v>
       </c>
       <c r="E96" t="s">
-        <v>261</v>
+        <v>166</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -4091,19 +4091,19 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>259</v>
+        <v>165</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>262</v>
+        <v>350</v>
       </c>
       <c r="E97" t="s">
-        <v>263</v>
+        <v>167</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -4117,19 +4117,19 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="B98" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="E98" t="s">
-        <v>266</v>
+        <v>169</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -4143,19 +4143,19 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="B99" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C99" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D99" t="s">
-        <v>267</v>
+        <v>352</v>
       </c>
       <c r="E99" t="s">
-        <v>268</v>
+        <v>170</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -4169,19 +4169,19 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>269</v>
+        <v>171</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="E100" t="s">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -4195,19 +4195,19 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>273</v>
+        <v>354</v>
       </c>
       <c r="E101" t="s">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -4221,19 +4221,19 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="B102" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D102" t="s">
-        <v>275</v>
+        <v>355</v>
       </c>
       <c r="E102" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -4247,19 +4247,19 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="B103" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>278</v>
+        <v>356</v>
       </c>
       <c r="E103" t="s">
-        <v>279</v>
+        <v>177</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4273,19 +4273,19 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C104" t="s">
         <v>10</v>
       </c>
       <c r="D104" t="s">
-        <v>280</v>
+        <v>357</v>
       </c>
       <c r="E104" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -4299,19 +4299,19 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D105" t="s">
-        <v>285</v>
+        <v>358</v>
       </c>
       <c r="E105" t="s">
-        <v>286</v>
+        <v>181</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -4325,19 +4325,19 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>282</v>
+        <v>179</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="E106" t="s">
-        <v>284</v>
+        <v>180</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -4351,19 +4351,19 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="B107" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C107" t="s">
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>288</v>
+        <v>360</v>
       </c>
       <c r="E107" t="s">
-        <v>289</v>
+        <v>183</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -4377,19 +4377,19 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="B108" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C108" t="s">
         <v>10</v>
       </c>
       <c r="D108" t="s">
-        <v>290</v>
+        <v>361</v>
       </c>
       <c r="E108" t="s">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -4403,19 +4403,19 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C109" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D109" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
       <c r="E109" t="s">
-        <v>296</v>
+        <v>187</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -4429,19 +4429,19 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>292</v>
+        <v>185</v>
       </c>
       <c r="B110" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C110" t="s">
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="E110" t="s">
-        <v>294</v>
+        <v>186</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -4455,19 +4455,19 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="B111" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C111" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D111" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="E111" t="s">
-        <v>301</v>
+        <v>190</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -4481,19 +4481,19 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>297</v>
+        <v>188</v>
       </c>
       <c r="B112" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C112" t="s">
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="E112" t="s">
-        <v>299</v>
+        <v>189</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -4507,19 +4507,19 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C113" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D113" t="s">
-        <v>305</v>
+        <v>366</v>
       </c>
       <c r="E113" t="s">
-        <v>306</v>
+        <v>193</v>
       </c>
       <c r="F113">
         <v>0</v>
@@ -4533,19 +4533,19 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="E114" t="s">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -4559,19 +4559,19 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>307</v>
+        <v>194</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C115" t="s">
         <v>10</v>
       </c>
       <c r="D115" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="E115" t="s">
-        <v>311</v>
+        <v>196</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -4585,19 +4585,19 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>307</v>
+        <v>194</v>
       </c>
       <c r="B116" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C116" t="s">
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="E116" t="s">
-        <v>309</v>
+        <v>195</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -4611,19 +4611,19 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>312</v>
+        <v>197</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D117" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="E117" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -4637,19 +4637,19 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>312</v>
+        <v>197</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C118" t="s">
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>313</v>
+        <v>371</v>
       </c>
       <c r="E118" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -4663,19 +4663,19 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>317</v>
+        <v>200</v>
       </c>
       <c r="B119" t="s">
         <v>8</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D119" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="E119" t="s">
-        <v>321</v>
+        <v>202</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>317</v>
+        <v>200</v>
       </c>
       <c r="B120" t="s">
         <v>8</v>
@@ -4698,10 +4698,10 @@
         <v>9</v>
       </c>
       <c r="D120" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="E120" t="s">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -4715,19 +4715,19 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>322</v>
+        <v>203</v>
       </c>
       <c r="B121" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C121" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D121" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
       <c r="E121" t="s">
-        <v>326</v>
+        <v>205</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -4741,19 +4741,19 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>322</v>
+        <v>203</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="C122" t="s">
         <v>10</v>
       </c>
       <c r="D122" t="s">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="E122" t="s">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -4767,19 +4767,19 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>327</v>
+        <v>206</v>
       </c>
       <c r="B123" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="E123" t="s">
-        <v>329</v>
+        <v>207</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -4793,19 +4793,19 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>327</v>
+        <v>206</v>
       </c>
       <c r="B124" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C124" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D124" t="s">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="E124" t="s">
-        <v>331</v>
+        <v>208</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -4819,19 +4819,19 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>332</v>
+        <v>209</v>
       </c>
       <c r="B125" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C125" t="s">
         <v>10</v>
       </c>
       <c r="D125" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="E125" t="s">
-        <v>336</v>
+        <v>211</v>
       </c>
       <c r="F125">
         <v>0</v>
@@ -4845,19 +4845,19 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>332</v>
+        <v>209</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C126" t="s">
         <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>333</v>
+        <v>379</v>
       </c>
       <c r="E126" t="s">
-        <v>334</v>
+        <v>210</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -4871,19 +4871,19 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>337</v>
+        <v>212</v>
       </c>
       <c r="B127" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C127" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D127" t="s">
-        <v>340</v>
+        <v>380</v>
       </c>
       <c r="E127" t="s">
-        <v>341</v>
+        <v>214</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -4897,19 +4897,19 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>337</v>
+        <v>212</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C128" t="s">
         <v>9</v>
       </c>
       <c r="D128" t="s">
-        <v>338</v>
+        <v>381</v>
       </c>
       <c r="E128" t="s">
-        <v>339</v>
+        <v>213</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -4923,19 +4923,19 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>342</v>
+        <v>215</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C129" t="s">
         <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="E129" t="s">
-        <v>344</v>
+        <v>216</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -4949,19 +4949,19 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>342</v>
+        <v>215</v>
       </c>
       <c r="B130" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C130" t="s">
         <v>10</v>
       </c>
       <c r="D130" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="E130" t="s">
-        <v>346</v>
+        <v>217</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -4975,19 +4975,19 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>347</v>
+        <v>218</v>
       </c>
       <c r="B131" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C131" t="s">
         <v>10</v>
       </c>
       <c r="D131" t="s">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="E131" t="s">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -5001,19 +5001,19 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>347</v>
+        <v>218</v>
       </c>
       <c r="B132" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C132" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D132" t="s">
-        <v>350</v>
+        <v>385</v>
       </c>
       <c r="E132" t="s">
-        <v>351</v>
+        <v>220</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -5027,19 +5027,19 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C133" t="s">
         <v>10</v>
       </c>
       <c r="D133" t="s">
-        <v>355</v>
+        <v>386</v>
       </c>
       <c r="E133" t="s">
-        <v>356</v>
+        <v>223</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -5053,19 +5053,19 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>352</v>
+        <v>221</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C134" t="s">
         <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>353</v>
+        <v>387</v>
       </c>
       <c r="E134" t="s">
-        <v>354</v>
+        <v>222</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -5079,19 +5079,19 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>357</v>
+        <v>224</v>
       </c>
       <c r="B135" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C135" t="s">
         <v>10</v>
       </c>
       <c r="D135" t="s">
-        <v>360</v>
+        <v>388</v>
       </c>
       <c r="E135" t="s">
-        <v>361</v>
+        <v>226</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -5105,19 +5105,19 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>357</v>
+        <v>224</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C136" t="s">
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>358</v>
+        <v>389</v>
       </c>
       <c r="E136" t="s">
-        <v>359</v>
+        <v>225</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -5131,19 +5131,19 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c r="B137" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C137" t="s">
         <v>10</v>
       </c>
       <c r="D137" t="s">
-        <v>365</v>
+        <v>390</v>
       </c>
       <c r="E137" t="s">
-        <v>366</v>
+        <v>229</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -5157,19 +5157,19 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c r="B138" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
       </c>
       <c r="D138" t="s">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="E138" t="s">
-        <v>364</v>
+        <v>228</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -5183,7 +5183,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>367</v>
+        <v>230</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
@@ -5192,10 +5192,10 @@
         <v>10</v>
       </c>
       <c r="D139" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="E139" t="s">
-        <v>371</v>
+        <v>232</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -5209,7 +5209,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>367</v>
+        <v>230</v>
       </c>
       <c r="B140" t="s">
         <v>8</v>
@@ -5218,10 +5218,10 @@
         <v>9</v>
       </c>
       <c r="D140" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="E140" t="s">
-        <v>369</v>
+        <v>231</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -5235,19 +5235,19 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>372</v>
+        <v>233</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C141" t="s">
         <v>9</v>
       </c>
       <c r="D141" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="E141" t="s">
-        <v>374</v>
+        <v>234</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -5261,19 +5261,19 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>372</v>
+        <v>233</v>
       </c>
       <c r="B142" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C142" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D142" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="E142" t="s">
-        <v>376</v>
+        <v>235</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -5287,19 +5287,19 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>377</v>
+        <v>236</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C143" t="s">
         <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="E143" t="s">
-        <v>379</v>
+        <v>237</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -5313,19 +5313,19 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>377</v>
+        <v>236</v>
       </c>
       <c r="B144" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C144" t="s">
         <v>10</v>
       </c>
       <c r="D144" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="E144" t="s">
-        <v>381</v>
+        <v>238</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -5339,19 +5339,19 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="B145" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C145" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D145" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="E145" t="s">
-        <v>386</v>
+        <v>241</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -5365,19 +5365,19 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>382</v>
+        <v>239</v>
       </c>
       <c r="B146" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
       </c>
       <c r="D146" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E146" t="s">
-        <v>384</v>
+        <v>240</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -5391,7 +5391,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>387</v>
+        <v>242</v>
       </c>
       <c r="B147" t="s">
         <v>8</v>
@@ -5400,10 +5400,10 @@
         <v>9</v>
       </c>
       <c r="D147" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="E147" t="s">
-        <v>389</v>
+        <v>243</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -5417,7 +5417,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>387</v>
+        <v>242</v>
       </c>
       <c r="B148" t="s">
         <v>8</v>
@@ -5426,10 +5426,10 @@
         <v>10</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E148" t="s">
-        <v>391</v>
+        <v>244</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -5443,19 +5443,19 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>392</v>
+        <v>245</v>
       </c>
       <c r="B149" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C149" t="s">
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E149" t="s">
-        <v>394</v>
+        <v>246</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -5469,19 +5469,19 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>392</v>
+        <v>245</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C150" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="E150" t="s">
-        <v>396</v>
+        <v>247</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -5495,19 +5495,19 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>397</v>
+        <v>248</v>
       </c>
       <c r="B151" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C151" t="s">
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E151" t="s">
-        <v>399</v>
+        <v>249</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -5521,19 +5521,19 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>397</v>
+        <v>248</v>
       </c>
       <c r="B152" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C152" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E152" t="s">
-        <v>401</v>
+        <v>250</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -5547,19 +5547,19 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="B153" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C153" t="s">
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E153" t="s">
-        <v>404</v>
+        <v>252</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -5573,19 +5573,19 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>402</v>
+        <v>251</v>
       </c>
       <c r="B154" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C154" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E154" t="s">
-        <v>406</v>
+        <v>253</v>
       </c>
       <c r="F154">
         <v>1</v>
